--- a/Exam/gymtrackerpro/lib/service/__tests__/bbt/exercise-service/listExercises-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/service/__tests__/bbt/exercise-service/listExercises-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="83">
-  <si>
-    <t>Statement: ExerciseService.listExercises(options?) – Delegates to exerciseRepository.findAll(options). Supports search, muscleGroup filter, includeInactive flag, and pagination.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="42">
+  <si>
+    <t>Statement: ExerciseService.listExercises(options)</t>
   </si>
   <si>
     <t/>
@@ -31,25 +31,25 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: ExerciseListOptions? { search?, muscleGroup?, includeInactive?, page?, pageSize? }</t>
+    <t>Input: options</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>exerciseRepository is accessible</t>
+    <t>repo accessible</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: Promise&lt;PageResult&lt;Exercise&gt;&gt; = { items: Exercise[], total: number }</t>
+    <t>Output: PageResult</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t>Returns filtered/paginated page of exercises.</t>
+    <t>Listed.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -64,36 +64,6 @@
     <t>Invalid EC</t>
   </si>
   <si>
-    <t>no options</t>
-  </si>
-  <si>
-    <t>returns page, passes undefined to repo</t>
-  </si>
-  <si>
-    <t>with options</t>
-  </si>
-  <si>
-    <t>search+muscleGroup passed through</t>
-  </si>
-  <si>
-    <t>includeInactive</t>
-  </si>
-  <si>
-    <t>true → all exercises returned</t>
-  </si>
-  <si>
-    <t>empty repo</t>
-  </si>
-  <si>
-    <t>items=[], total=0</t>
-  </si>
-  <si>
-    <t>pagination</t>
-  </si>
-  <si>
-    <t>page/pageSize passed through</t>
-  </si>
-  <si>
     <t>No TC</t>
   </si>
   <si>
@@ -109,121 +79,28 @@
     <t>Actual Result</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>no options, repo returns 1 exercise</t>
-  </si>
-  <si>
-    <t>items.length=1, total=1; findAll(undefined) called</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>{ search: "Bench", muscleGroup: CHEST, page: 1, pageSize: 10 }</t>
-  </si>
-  <si>
-    <t>findAll called with those options</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>{ includeInactive: true }, repo returns 2 items</t>
-  </si>
-  <si>
-    <t>total=2; findAll(options) called</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>no options, repo returns empty</t>
-  </si>
-  <si>
-    <t>items.length=0, total=0; findAll(undefined) called</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>{ page: 2, pageSize: 5 }</t>
-  </si>
-  <si>
-    <t>findAll({ page:2, pageSize:5 }) called</t>
-  </si>
-  <si>
     <t>Number BVA</t>
   </si>
   <si>
     <t>BVA Test Case</t>
   </si>
   <si>
-    <t>includeInactive boundary</t>
-  </si>
-  <si>
-    <t>includeInactive=false (default) → active only; includeInactive=true → all</t>
-  </si>
-  <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>includeInactive=true</t>
-  </si>
-  <si>
-    <t>{ includeInactive: true }, 1 active + 1 inactive</t>
-  </si>
-  <si>
-    <t>total=2</t>
-  </si>
-  <si>
     <t>TC from EC</t>
   </si>
   <si>
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>EP-1</t>
-  </si>
-  <si>
-    <t>No options, 1 exercise</t>
-  </si>
-  <si>
-    <t>items.length=1, total=1</t>
-  </si>
-  <si>
-    <t>EP-2</t>
-  </si>
-  <si>
-    <t>search + muscleGroup options</t>
-  </si>
-  <si>
-    <t>findAll called with options</t>
-  </si>
-  <si>
-    <t>EP-3</t>
-  </si>
-  <si>
-    <t>BVA-1</t>
-  </si>
-  <si>
-    <t>includeInactive=true, 2 in repo</t>
-  </si>
-  <si>
-    <t>EP-4</t>
-  </si>
-  <si>
-    <t>Empty repo</t>
-  </si>
-  <si>
-    <t>EP-5</t>
-  </si>
-  <si>
-    <t>page=2, pageSize=5</t>
-  </si>
-  <si>
-    <t>findAll called with pagination</t>
+    <t>List</t>
+  </si>
+  <si>
+    <t>Success</t>
+  </si>
+  <si>
+    <t>Passed</t>
   </si>
   <si>
     <t>Testing</t>
@@ -781,7 +658,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -803,76 +680,6 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -881,7 +688,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -893,104 +700,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1001,7 +723,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1011,24 +733,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1039,7 +750,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1051,36 +762,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1091,7 +785,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1104,22 +798,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1127,19 +821,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1147,19 +841,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1167,19 +861,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>61</v>
+        <v>16</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1187,19 +881,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1207,19 +901,439 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>68</v>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1247,16 +1361,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1264,45 +1378,45 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>74</v>
+        <v>33</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>74</v>
+        <v>33</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>75</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="B3" s="1">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="C3" s="1">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -1311,19 +1425,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/Exam/gymtrackerpro/lib/service/__tests__/bbt/exercise-service/listExercises-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/service/__tests__/bbt/exercise-service/listExercises-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="42">
-  <si>
-    <t>Statement: ExerciseService.listExercises(options)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="114">
+  <si>
+    <t>Statement: ExerciseService.listExercises(options) – Returns a paginated list of exercises. Supports optional filtering by search term, muscle group, and active status. Results are ordered by name ascending. By default only active exercises are returned.</t>
   </si>
   <si>
     <t/>
@@ -31,25 +31,25 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: options</t>
+    <t>Input: ExerciseListOptions { search?: string, muscleGroup?: MuscleGroup, includeInactive?: boolean, page?: number, pageSize?: number }</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>repo accessible</t>
+    <t>Exercises may or may not exist in the system. All options fields are optional.</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: PageResult</t>
+    <t>Output: Promise&lt;PageResult&lt;Exercise&gt;&gt;</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t>Listed.</t>
+    <t>On success: PageResult returned with items and total matching the provided options. Items ordered by name ascending.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -64,6 +64,39 @@
     <t>Invalid EC</t>
   </si>
   <si>
+    <t>Inactive inclusion</t>
+  </si>
+  <si>
+    <t>includeInactive: true → all exercises (active + inactive) returned</t>
+  </si>
+  <si>
+    <t>includeInactive: false or undefined → only active exercises returned</t>
+  </si>
+  <si>
+    <t>Muscle group filter</t>
+  </si>
+  <si>
+    <t>Valid MuscleGroup provided → filtered by muscle group</t>
+  </si>
+  <si>
+    <t>No muscle group filter → all active exercises returned</t>
+  </si>
+  <si>
+    <t>Search term</t>
+  </si>
+  <si>
+    <t>Search term + muscle group filter → filtered results returned</t>
+  </si>
+  <si>
+    <t>Data availability</t>
+  </si>
+  <si>
+    <t>Multiple exercises → ordered by name ascending</t>
+  </si>
+  <si>
+    <t>Empty options → all active exercises returned</t>
+  </si>
+  <si>
     <t>No TC</t>
   </si>
   <si>
@@ -79,30 +112,213 @@
     <t>Actual Result</t>
   </si>
   <si>
+    <t>EC-2</t>
+  </si>
+  <si>
+    <t>No options</t>
+  </si>
+  <si>
+    <t>PageResult with active exercises only, items and total returned</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>includeInactive: false</t>
+  </si>
+  <si>
+    <t>EC-1</t>
+  </si>
+  <si>
+    <t>includeInactive: true</t>
+  </si>
+  <si>
+    <t>PageResult containing both active and inactive exercises, total: 2</t>
+  </si>
+  <si>
+    <t>EC-3</t>
+  </si>
+  <si>
+    <t>muscleGroup: BACK</t>
+  </si>
+  <si>
+    <t>PageResult with exercises filtered to BACK muscle group</t>
+  </si>
+  <si>
+    <t>EC-5</t>
+  </si>
+  <si>
+    <t>search: "Bench", muscleGroup: CHEST</t>
+  </si>
+  <si>
+    <t>PageResult with exercises matching both filters</t>
+  </si>
+  <si>
+    <t>EC-6</t>
+  </si>
+  <si>
+    <t>Multiple exercises in DB</t>
+  </si>
+  <si>
+    <t>PageResult items[0].name: "Deadlift", items[1].name: "Standard Bench Press"</t>
+  </si>
+  <si>
+    <t>EC-7</t>
+  </si>
+  <si>
+    <t>options: {}</t>
+  </si>
+  <si>
+    <t>PageResult with all active exercises, items and total returned</t>
+  </si>
+  <si>
     <t>Number BVA</t>
   </si>
   <si>
     <t>BVA Test Case</t>
   </si>
   <si>
+    <t>Search term length</t>
+  </si>
+  <si>
+    <t>undefined, "" (empty), "a" (1 char)</t>
+  </si>
+  <si>
+    <t>Muscle group values</t>
+  </si>
+  <si>
+    <t>CHEST, SHOULDERS, ARMS, BACK, CORE, LEGS, "INVALID" (unknown value)</t>
+  </si>
+  <si>
+    <t>includeInactive flag</t>
+  </si>
+  <si>
+    <t>undefined, false, true</t>
+  </si>
+  <si>
+    <t>Page number</t>
+  </si>
+  <si>
+    <t>undefined, 0 (treated as page 1), 1 (first page), 2 (second page)</t>
+  </si>
+  <si>
+    <t>Page size</t>
+  </si>
+  <si>
+    <t>undefined (default size), 0 (no items), 1 (one item)</t>
+  </si>
+  <si>
     <t>BVA</t>
   </si>
   <si>
+    <t>BVA-1</t>
+  </si>
+  <si>
+    <t>search: undefined</t>
+  </si>
+  <si>
+    <t>PageResult returned with items and total</t>
+  </si>
+  <si>
+    <t>search: ""</t>
+  </si>
+  <si>
+    <t>search: "a"</t>
+  </si>
+  <si>
+    <t>PageResult returned with matching items and total</t>
+  </si>
+  <si>
+    <t>BVA-2</t>
+  </si>
+  <si>
+    <t>muscleGroup: CHEST</t>
+  </si>
+  <si>
+    <t>PageResult with 1 item, items[0].muscleGroup: CHEST</t>
+  </si>
+  <si>
+    <t>muscleGroup: SHOULDERS</t>
+  </si>
+  <si>
+    <t>PageResult with no items, total: 0</t>
+  </si>
+  <si>
+    <t>muscleGroup: ARMS</t>
+  </si>
+  <si>
+    <t>PageResult with 1 item, items[0].muscleGroup: BACK</t>
+  </si>
+  <si>
+    <t>muscleGroup: CORE</t>
+  </si>
+  <si>
+    <t>PageResult with no items</t>
+  </si>
+  <si>
+    <t>muscleGroup: LEGS</t>
+  </si>
+  <si>
+    <t>muscleGroup: "INVALID"</t>
+  </si>
+  <si>
+    <t>BVA-3</t>
+  </si>
+  <si>
+    <t>includeInactive: undefined</t>
+  </si>
+  <si>
+    <t>PageResult with 1 active item, items[0].isActive: true</t>
+  </si>
+  <si>
+    <t>BVA-4</t>
+  </si>
+  <si>
+    <t>page: undefined</t>
+  </si>
+  <si>
+    <t>PageResult with page 1 items</t>
+  </si>
+  <si>
+    <t>page: 0</t>
+  </si>
+  <si>
+    <t>page: 1</t>
+  </si>
+  <si>
+    <t>page: 2, pageSize: 10</t>
+  </si>
+  <si>
+    <t>PageResult with page 2 items, total: 11</t>
+  </si>
+  <si>
+    <t>BVA-5</t>
+  </si>
+  <si>
+    <t>pageSize: undefined</t>
+  </si>
+  <si>
+    <t>PageResult with default page size applied</t>
+  </si>
+  <si>
+    <t>pageSize: 0</t>
+  </si>
+  <si>
+    <t>PageResult with no items on page, total reflects full count</t>
+  </si>
+  <si>
+    <t>pageSize: 1</t>
+  </si>
+  <si>
+    <t>PageResult with exactly 1 item on page, total reflects full count</t>
+  </si>
+  <si>
     <t>TC from EC</t>
   </si>
   <si>
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>List</t>
-  </si>
-  <si>
-    <t>Success</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
     <t>Testing</t>
   </si>
   <si>
@@ -133,7 +349,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>EXM-02/EXM-06</t>
+    <t>SERV-17</t>
   </si>
   <si>
     <t>n/a</t>
@@ -658,7 +874,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -680,6 +896,104 @@
         <v>14</v>
       </c>
     </row>
+    <row r="2" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -688,7 +1002,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -700,19 +1014,138 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>19</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -723,7 +1156,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -733,13 +1166,68 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>21</v>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -750,7 +1238,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -762,19 +1250,359 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="B16" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="B18" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="B19" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
         <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -798,22 +1626,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>23</v>
+        <v>98</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -821,19 +1649,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -841,19 +1669,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -861,19 +1689,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -881,19 +1709,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -901,19 +1729,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -921,19 +1749,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -941,19 +1769,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -961,19 +1789,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -981,19 +1809,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1001,19 +1829,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1021,19 +1849,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1041,19 +1869,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1061,19 +1889,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1081,19 +1909,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>26</v>
+        <v>76</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1101,19 +1929,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1121,19 +1949,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1141,19 +1969,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1161,19 +1989,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1181,19 +2009,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1201,19 +2029,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1221,19 +2049,19 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1241,19 +2069,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>25</v>
+        <v>87</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1261,19 +2089,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>25</v>
+        <v>88</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1281,19 +2109,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>25</v>
+        <v>89</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1301,19 +2129,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>25</v>
+        <v>92</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>26</v>
+        <v>93</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1321,19 +2149,19 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>25</v>
+        <v>94</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>26</v>
+        <v>95</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1361,16 +2189,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>29</v>
+        <v>101</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>30</v>
+        <v>102</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1378,39 +2206,39 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>32</v>
+        <v>104</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>33</v>
+        <v>105</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>35</v>
+        <v>107</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>32</v>
+        <v>104</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>33</v>
+        <v>105</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>38</v>
+        <v>110</v>
       </c>
       <c r="B3" s="1">
         <v>26</v>
@@ -1425,19 +2253,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>39</v>
+        <v>111</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>40</v>
+        <v>112</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>41</v>
+        <v>113</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>41</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/Exam/gymtrackerpro/lib/service/__tests__/bbt/exercise-service/listExercises-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/service/__tests__/bbt/exercise-service/listExercises-bbt-form.xlsx
@@ -349,7 +349,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>SERV-17</t>
+    <t>SERV-18</t>
   </si>
   <si>
     <t>n/a</t>
